--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="439">
   <si>
     <t/>
   </si>
@@ -305,6 +305,24 @@
   </si>
   <si>
     <t>MARLBORO BLACK 16'S</t>
+  </si>
+  <si>
+    <t>20142598</t>
+  </si>
+  <si>
+    <t>MARLBORO MOTION 16'S</t>
+  </si>
+  <si>
+    <t>20142606</t>
+  </si>
+  <si>
+    <t>MARLBORO MOTION 12'S</t>
+  </si>
+  <si>
+    <t>20142607</t>
+  </si>
+  <si>
+    <t>FILTER MOTION 20'S</t>
   </si>
   <si>
     <t>20125676</t>
@@ -1702,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2526,10 +2544,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,10 +2564,10 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2566,18 +2584,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>104</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2586,18 +2604,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2606,18 +2624,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2626,10 +2644,10 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2646,10 +2664,10 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,13 +2681,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,13 +2701,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,10 +2721,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2726,7 +2744,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2746,10 +2764,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,7 +2784,7 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2786,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2806,7 +2824,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2826,10 +2844,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,10 +2864,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2886,10 +2904,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2906,10 +2924,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,7 +2944,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2946,7 +2964,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2963,10 +2981,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2983,10 +3001,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3003,10 +3021,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3026,7 +3044,7 @@
         <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3046,7 +3064,7 @@
         <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3066,7 +3084,7 @@
         <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3086,7 +3104,7 @@
         <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3106,7 +3124,7 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3123,10 +3141,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3143,10 +3161,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3163,10 +3181,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3186,7 +3204,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3206,7 +3224,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3226,7 +3244,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3246,7 +3264,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3266,7 +3284,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3286,7 +3304,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3306,7 +3324,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3326,7 +3344,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3346,7 +3364,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3366,7 +3384,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3386,7 +3404,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3403,10 +3421,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3423,10 +3441,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3443,10 +3461,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3466,7 +3484,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3486,7 +3504,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3506,7 +3524,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3526,10 +3544,10 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,7 +3564,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3566,7 +3584,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3586,10 +3604,10 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3603,10 +3621,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3623,10 +3641,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3643,10 +3661,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3666,7 +3684,7 @@
         <v>30</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3686,7 +3704,7 @@
         <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3706,7 +3724,7 @@
         <v>30</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3726,7 +3744,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3746,7 +3764,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3766,7 +3784,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3786,7 +3804,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3806,10 +3824,10 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3826,7 +3844,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3846,10 +3864,10 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,10 +3884,10 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3883,10 +3901,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3903,13 +3921,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3923,13 +3941,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3986,7 +4004,7 @@
         <v>33</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4006,7 +4024,7 @@
         <v>33</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4026,7 +4044,7 @@
         <v>33</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4046,7 +4064,7 @@
         <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4066,7 +4084,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4086,7 +4104,7 @@
         <v>33</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4109,7 +4127,7 @@
         <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4126,7 +4144,7 @@
         <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4146,7 +4164,7 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4166,10 +4184,10 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4209,7 +4227,7 @@
         <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,10 +4284,10 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,7 +4304,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4306,7 +4324,7 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4329,7 +4347,7 @@
         <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4349,7 +4367,7 @@
         <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4369,7 +4387,7 @@
         <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4389,7 +4407,7 @@
         <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,7 +4427,7 @@
         <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4429,7 +4447,7 @@
         <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4529,7 +4547,7 @@
         <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4546,10 +4564,10 @@
         <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4566,10 +4584,10 @@
         <v>33</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,7 +4604,7 @@
         <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>9</v>
@@ -4629,7 +4647,7 @@
         <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4649,7 +4667,7 @@
         <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4669,7 +4687,7 @@
         <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4726,7 +4744,7 @@
         <v>33</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4743,10 +4761,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4763,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4783,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4806,7 +4824,7 @@
         <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4826,7 +4844,7 @@
         <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4846,7 +4864,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4866,7 +4884,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4886,7 +4904,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4906,7 +4924,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4926,7 +4944,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4946,10 +4964,10 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4966,7 +4984,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4986,10 +5004,10 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5003,13 +5021,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5023,10 +5041,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5043,13 +5061,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5066,7 +5084,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5086,7 +5104,7 @@
         <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5106,7 +5124,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5126,7 +5144,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5146,7 +5164,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5166,7 +5184,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5186,7 +5204,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5206,7 +5224,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5226,7 +5244,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5246,7 +5264,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5263,10 +5281,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5283,10 +5301,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5303,10 +5321,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5326,7 +5344,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5346,7 +5364,7 @@
         <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5366,10 +5384,10 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5386,10 +5404,10 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5406,10 +5424,10 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5426,10 +5444,10 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5446,10 +5464,10 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5466,10 +5484,10 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5486,7 +5504,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5506,7 +5524,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5526,7 +5544,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5546,7 +5564,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5563,10 +5581,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5583,10 +5601,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5603,10 +5621,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5626,7 +5644,7 @@
         <v>84</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5646,7 +5664,7 @@
         <v>84</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5666,7 +5684,7 @@
         <v>84</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5686,7 +5704,7 @@
         <v>84</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5703,10 +5721,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5723,10 +5741,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5743,10 +5761,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5766,7 +5784,7 @@
         <v>87</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5786,7 +5804,7 @@
         <v>87</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5806,7 +5824,7 @@
         <v>87</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5826,7 +5844,7 @@
         <v>87</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5846,9 +5864,69 @@
         <v>87</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F207" s="1" t="s">
+      <c r="F210" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="443">
   <si>
     <t/>
   </si>
@@ -508,6 +508,12 @@
     <t>DJARUM76 MGA RYL12'S</t>
   </si>
   <si>
+    <t>20142672</t>
+  </si>
+  <si>
+    <t>DJARUM BLCK MTCHA 12</t>
+  </si>
+  <si>
     <t>20084820</t>
   </si>
   <si>
@@ -932,6 +938,12 @@
   </si>
   <si>
     <t>VEEVA PODS GRAPE</t>
+  </si>
+  <si>
+    <t>20142671</t>
+  </si>
+  <si>
+    <t>VEEVA ULTRA CHERRY</t>
   </si>
   <si>
     <t>20137962</t>
@@ -1720,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3201,10 +3213,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3224,7 +3236,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3244,7 +3256,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3264,7 +3276,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3284,7 +3296,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3304,7 +3316,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3324,7 +3336,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3344,7 +3356,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3364,7 +3376,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3384,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3404,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3424,7 +3436,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3444,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3464,7 +3476,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3481,10 +3493,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3504,7 +3516,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3524,7 +3536,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3544,7 +3556,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3564,7 +3576,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3584,7 +3596,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3604,10 +3616,10 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3624,10 +3636,10 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3644,7 +3656,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3664,7 +3676,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3681,10 +3693,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3704,7 +3716,7 @@
         <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3724,7 +3736,7 @@
         <v>30</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3744,7 +3756,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3764,7 +3776,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3784,7 +3796,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3804,7 +3816,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3824,7 +3836,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3844,7 +3856,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3864,7 +3876,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3884,10 +3896,10 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,10 +3916,10 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,10 +3936,10 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,7 +3956,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>9</v>
@@ -3961,13 +3973,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4064,7 +4076,7 @@
         <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4124,7 +4136,7 @@
         <v>33</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4187,7 +4199,7 @@
         <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4204,10 +4216,10 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4287,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4307,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4344,7 +4356,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4407,7 +4419,7 @@
         <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4467,7 +4479,7 @@
         <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4607,7 +4619,7 @@
         <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,7 +4636,7 @@
         <v>33</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>9</v>
@@ -4644,10 +4656,10 @@
         <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4707,7 +4719,7 @@
         <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4727,7 +4739,7 @@
         <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4804,7 +4816,7 @@
         <v>33</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4821,10 +4833,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4841,10 +4853,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4864,7 +4876,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4884,7 +4896,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4904,7 +4916,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4924,7 +4936,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4944,7 +4956,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4964,7 +4976,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4984,7 +4996,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5004,7 +5016,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5024,10 +5036,10 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5044,7 +5056,7 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5064,7 +5076,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5081,10 +5093,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5101,13 +5113,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5124,7 +5136,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5144,7 +5156,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5164,7 +5176,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5184,7 +5196,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5204,7 +5216,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5224,7 +5236,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5244,7 +5256,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5264,7 +5276,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5284,7 +5296,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5304,7 +5316,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5324,7 +5336,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5341,10 +5353,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5361,10 +5373,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5384,7 +5396,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5404,7 +5416,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5424,7 +5436,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5444,10 +5456,10 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5464,10 +5476,10 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5484,7 +5496,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>9</v>
@@ -5504,10 +5516,10 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5524,10 +5536,10 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5544,7 +5556,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5564,7 +5576,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5584,7 +5596,7 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5604,7 +5616,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5624,7 +5636,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5641,10 +5653,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5661,10 +5673,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5684,7 +5696,7 @@
         <v>84</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5704,7 +5716,7 @@
         <v>84</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5724,7 +5736,7 @@
         <v>84</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5744,7 +5756,7 @@
         <v>84</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5764,7 +5776,7 @@
         <v>84</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5781,10 +5793,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5801,10 +5813,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5824,7 +5836,7 @@
         <v>87</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5844,7 +5856,7 @@
         <v>87</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5864,7 +5876,7 @@
         <v>87</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5884,7 +5896,7 @@
         <v>87</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5904,7 +5916,7 @@
         <v>87</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5924,9 +5936,49 @@
         <v>87</v>
       </c>
       <c r="E210" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F210" s="1" t="s">
+      <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="441">
   <si>
     <t/>
   </si>
@@ -980,12 +980,6 @@
   </si>
   <si>
     <t>VEEV NOW ULTR STR CL</t>
-  </si>
-  <si>
-    <t>20138764</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTR PDN CF</t>
   </si>
   <si>
     <t>20139526</t>
@@ -1732,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4836,7 +4830,7 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4853,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4876,7 +4870,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4896,7 +4890,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4916,7 +4910,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4936,7 +4930,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4956,7 +4950,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4976,7 +4970,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4996,7 +4990,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5016,7 +5010,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5036,7 +5030,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5056,10 +5050,10 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5076,10 +5070,10 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,10 +5090,10 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,13 +5107,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5136,7 +5130,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5156,7 +5150,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5176,7 +5170,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5196,7 +5190,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5216,7 +5210,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5236,7 +5230,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5256,7 +5250,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5276,7 +5270,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5296,7 +5290,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5316,7 +5310,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5336,7 +5330,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5356,7 +5350,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5373,10 +5367,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5396,7 +5390,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5416,7 +5410,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5436,7 +5430,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5456,7 +5450,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5476,10 +5470,10 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5496,7 +5490,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>9</v>
@@ -5516,7 +5510,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>9</v>
@@ -5536,10 +5530,10 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5556,7 +5550,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5576,7 +5570,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5596,7 +5590,7 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5616,7 +5610,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5636,7 +5630,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5656,7 +5650,7 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5673,10 +5667,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5696,7 +5690,7 @@
         <v>84</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5716,7 +5710,7 @@
         <v>84</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5736,7 +5730,7 @@
         <v>84</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5756,7 +5750,7 @@
         <v>84</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5776,7 +5770,7 @@
         <v>84</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5796,7 +5790,7 @@
         <v>84</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5813,10 +5807,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5836,7 +5830,7 @@
         <v>87</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5856,7 +5850,7 @@
         <v>87</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5876,7 +5870,7 @@
         <v>87</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5896,7 +5890,7 @@
         <v>87</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5916,7 +5910,7 @@
         <v>87</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5936,7 +5930,7 @@
         <v>87</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5956,29 +5950,9 @@
         <v>87</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="443">
   <si>
     <t/>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>DUFF FILTER BOLD20'S</t>
+  </si>
+  <si>
+    <t>20142836</t>
+  </si>
+  <si>
+    <t>TWIZZ TROP.CRSH 20'S</t>
   </si>
   <si>
     <t>10010094</t>
@@ -1726,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2147,10 +2153,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2170,7 +2176,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2190,10 +2196,10 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,10 +2216,10 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2250,10 +2256,10 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,10 +2276,10 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,7 +2296,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2310,7 +2316,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2330,7 +2336,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2350,10 +2356,10 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,7 +2396,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2410,7 +2416,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2418,10 +2424,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2430,7 +2436,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2438,19 +2444,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2470,7 +2476,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2490,10 +2496,10 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,10 +2516,10 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2550,10 +2556,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2570,7 +2576,7 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>9</v>
@@ -2590,7 +2596,7 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>9</v>
@@ -2610,10 +2616,10 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2630,10 +2636,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2650,18 +2656,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2670,10 +2676,10 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2690,10 +2696,10 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2710,10 +2716,10 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2730,7 +2736,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2747,10 +2753,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2770,10 +2776,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2790,10 +2796,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2810,7 +2816,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2830,7 +2836,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2850,7 +2856,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2870,7 +2876,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2890,7 +2896,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2910,10 +2916,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2930,10 +2936,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2950,10 +2956,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2970,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2990,7 +2996,7 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3010,7 +3016,7 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3030,7 +3036,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3047,10 +3053,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3070,7 +3076,7 @@
         <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3090,7 +3096,7 @@
         <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3110,7 +3116,7 @@
         <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3130,7 +3136,7 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3150,7 +3156,7 @@
         <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3170,7 +3176,7 @@
         <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3190,7 +3196,7 @@
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3210,7 +3216,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3227,10 +3233,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3250,7 +3256,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3270,7 +3276,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3290,7 +3296,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3310,7 +3316,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3330,7 +3336,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3350,7 +3356,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3370,7 +3376,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3390,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3410,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3430,7 +3436,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3450,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3470,7 +3476,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3490,7 +3496,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3507,10 +3513,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3530,7 +3536,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3550,7 +3556,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3570,7 +3576,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3590,7 +3596,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3610,7 +3616,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3630,10 +3636,10 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3650,10 +3656,10 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,7 +3676,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3690,7 +3696,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3707,10 +3713,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3730,7 +3736,7 @@
         <v>30</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3750,7 +3756,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3770,7 +3776,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3790,7 +3796,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3810,7 +3816,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3830,7 +3836,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3850,7 +3856,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3870,7 +3876,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3890,7 +3896,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3910,10 +3916,10 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,10 +3936,10 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,10 +3956,10 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3970,7 +3976,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>9</v>
@@ -3987,13 +3993,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4090,7 +4096,7 @@
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4150,7 +4156,7 @@
         <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4213,7 +4219,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4230,10 +4236,10 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4339,7 @@
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4370,7 +4376,7 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4433,7 +4439,7 @@
         <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,7 +4499,7 @@
         <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,7 +4639,7 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,7 +4659,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4670,10 +4676,10 @@
         <v>33</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,7 +4759,7 @@
         <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4830,7 +4836,7 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4847,10 +4853,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4870,7 +4876,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4890,7 +4896,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4910,7 +4916,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4930,7 +4936,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4950,7 +4956,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4970,7 +4976,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4990,7 +4996,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5010,7 +5016,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5030,7 +5036,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5050,10 +5056,10 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5070,10 +5076,10 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5090,10 +5096,10 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5107,13 +5113,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5130,7 +5136,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5150,7 +5156,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5170,7 +5176,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5190,7 +5196,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5210,7 +5216,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5230,7 +5236,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5250,7 +5256,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5270,7 +5276,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5290,7 +5296,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5310,7 +5316,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5330,7 +5336,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5350,7 +5356,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5367,10 +5373,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5390,7 +5396,7 @@
         <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5410,7 +5416,7 @@
         <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5430,7 +5436,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5450,7 +5456,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5470,10 +5476,10 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5490,7 +5496,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>9</v>
@@ -5510,7 +5516,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>9</v>
@@ -5530,10 +5536,10 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5550,7 +5556,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5570,7 +5576,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5590,7 +5596,7 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5610,7 +5616,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5630,7 +5636,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5650,7 +5656,7 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5667,10 +5673,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5687,10 +5693,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5707,10 +5713,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5727,10 +5733,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5747,10 +5753,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5767,10 +5773,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5787,10 +5793,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5807,10 +5813,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5827,10 +5833,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5847,10 +5853,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5867,10 +5873,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5887,10 +5893,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5907,10 +5913,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5927,10 +5933,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5947,12 +5953,32 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E211" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F211" s="1" t="s">
+      <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="445">
   <si>
     <t/>
   </si>
@@ -898,12 +898,6 @@
     <t>VEEV ONE1000 GRAPE</t>
   </si>
   <si>
-    <t>20138765</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 STRW CL</t>
-  </si>
-  <si>
     <t>20139616</t>
   </si>
   <si>
@@ -1162,6 +1156,12 @@
     <t>ESSE FILTER BLUE 20S</t>
   </si>
   <si>
+    <t>20126307</t>
+  </si>
+  <si>
+    <t>ESSE DOUBLE POP 16'S</t>
+  </si>
+  <si>
     <t>20138128</t>
   </si>
   <si>
@@ -1246,10 +1246,10 @@
     <t>ESSE CHNG DOUB 20'S</t>
   </si>
   <si>
-    <t>20126307</t>
-  </si>
-  <si>
-    <t>ESSE DOUBLE POP 16'S</t>
+    <t>20143095</t>
+  </si>
+  <si>
+    <t>ESSE CHG DBL PINPL20</t>
   </si>
   <si>
     <t>20038143</t>
@@ -1340,6 +1340,12 @@
   </si>
   <si>
     <t>GG SURYA MERAH 16S</t>
+  </si>
+  <si>
+    <t>20143093</t>
+  </si>
+  <si>
+    <t>GG KRETEK MRH NEW 12</t>
   </si>
 </sst>
 </file>
@@ -1732,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4639,7 +4645,7 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,7 +4665,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4676,10 +4682,10 @@
         <v>33</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,7 +4765,7 @@
         <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4836,7 +4842,7 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4853,10 +4859,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4876,7 +4882,7 @@
         <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4896,7 +4902,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4916,7 +4922,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4936,7 +4942,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4956,7 +4962,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4976,7 +4982,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4996,7 +5002,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5016,7 +5022,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5036,7 +5042,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5056,10 +5062,10 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5076,10 +5082,10 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,10 +5102,10 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,13 +5119,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5136,7 +5142,7 @@
         <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5156,7 +5162,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5176,7 +5182,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5196,7 +5202,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5216,7 +5222,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5236,7 +5242,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5256,7 +5262,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5276,7 +5282,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5296,7 +5302,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5316,7 +5322,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5336,7 +5342,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5356,7 +5362,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5376,7 +5382,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5979,6 +5985,26 @@
         <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="449">
   <si>
     <t/>
   </si>
@@ -944,6 +944,18 @@
   </si>
   <si>
     <t>VEEVA ULTRA CHERRY</t>
+  </si>
+  <si>
+    <t>20143055</t>
+  </si>
+  <si>
+    <t>VEEVA POD BLUBERY500</t>
+  </si>
+  <si>
+    <t>20143072</t>
+  </si>
+  <si>
+    <t>VEEVA SOUR APPLE500</t>
   </si>
   <si>
     <t>20137962</t>
@@ -1738,7 +1750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4682,7 +4694,7 @@
         <v>33</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>9</v>
@@ -4702,7 +4714,7 @@
         <v>33</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>9</v>
@@ -4765,7 +4777,7 @@
         <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4785,7 +4797,7 @@
         <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4842,7 +4854,7 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4859,10 +4871,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4879,10 +4891,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4902,7 +4914,7 @@
         <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4922,7 +4934,7 @@
         <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4942,7 +4954,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4962,7 +4974,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4982,7 +4994,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5002,7 +5014,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5022,7 +5034,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5042,7 +5054,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5062,10 +5074,10 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5082,7 +5094,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5102,7 +5114,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>9</v>
@@ -5119,10 +5131,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5139,13 +5151,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5162,7 +5174,7 @@
         <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5182,7 +5194,7 @@
         <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5202,7 +5214,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5222,7 +5234,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5242,7 +5254,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5262,7 +5274,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5282,7 +5294,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5302,7 +5314,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5322,7 +5334,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5342,7 +5354,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5362,7 +5374,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5382,7 +5394,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5399,10 +5411,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5419,10 +5431,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5442,7 +5454,7 @@
         <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5462,7 +5474,7 @@
         <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5482,7 +5494,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5502,10 +5514,10 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5522,10 +5534,10 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,7 +5554,7 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>9</v>
@@ -5562,10 +5574,10 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5582,10 +5594,10 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5602,7 +5614,7 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5622,7 +5634,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5642,7 +5654,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5662,7 +5674,7 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5682,7 +5694,7 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5699,10 +5711,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5719,10 +5731,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5742,7 +5754,7 @@
         <v>86</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5762,7 +5774,7 @@
         <v>86</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5782,7 +5794,7 @@
         <v>86</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5802,7 +5814,7 @@
         <v>86</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5822,7 +5834,7 @@
         <v>86</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5839,10 +5851,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5859,10 +5871,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5882,7 +5894,7 @@
         <v>89</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5902,7 +5914,7 @@
         <v>89</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5922,7 +5934,7 @@
         <v>89</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5942,7 +5954,7 @@
         <v>89</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5962,7 +5974,7 @@
         <v>89</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -5982,7 +5994,7 @@
         <v>89</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6002,9 +6014,49 @@
         <v>89</v>
       </c>
       <c r="E213" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F213" s="1" t="s">
+      <c r="F215" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="456">
   <si>
     <t/>
   </si>
@@ -520,6 +520,12 @@
     <t>DJARUM BLCK MTCHA 12</t>
   </si>
   <si>
+    <t>20143204</t>
+  </si>
+  <si>
+    <t>T/M FLTR COOL BRY16</t>
+  </si>
+  <si>
     <t>20084820</t>
   </si>
   <si>
@@ -700,6 +706,12 @@
     <t>DIPLOMAT EVO16'S</t>
   </si>
   <si>
+    <t>20143212</t>
+  </si>
+  <si>
+    <t>3VO CLICK MATCHA16S</t>
+  </si>
+  <si>
     <t>20141244</t>
   </si>
   <si>
@@ -736,16 +748,25 @@
     <t>IDM LGHT CRCKT ELKTR</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20142352</t>
   </si>
   <si>
     <t>IDM UTILITY LIGHTER</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20142409</t>
   </si>
   <si>
     <t>IDM LIGHTER EL M2000</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>20128084</t>
@@ -1750,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F215"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3271,10 +3292,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3294,7 +3315,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3314,7 +3335,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3334,7 +3355,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3354,7 +3375,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3374,7 +3395,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3394,7 +3415,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3414,7 +3435,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3434,7 +3455,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3454,7 +3475,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3474,7 +3495,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3494,7 +3515,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3514,7 +3535,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3534,7 +3555,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3551,10 +3572,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3574,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3594,7 +3615,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3614,7 +3635,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3634,7 +3655,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3654,7 +3675,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3674,10 +3695,10 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,10 +3715,10 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3714,7 +3735,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3734,7 +3755,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3751,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3774,7 +3795,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3794,7 +3815,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3814,7 +3835,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3834,7 +3855,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3854,7 +3875,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3874,7 +3895,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3894,7 +3915,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3914,7 +3935,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3934,7 +3955,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3954,10 +3975,10 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,7 +3995,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3994,10 +4015,10 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,58 +4035,58 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>89</v>
+        <v>245</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -4082,10 +4103,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4102,10 +4123,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4122,10 +4143,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4134,7 +4155,7 @@
         <v>33</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4142,10 +4163,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4154,7 +4175,7 @@
         <v>33</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4162,10 +4183,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4182,10 +4203,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4194,7 +4215,7 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4202,10 +4223,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4214,7 +4235,7 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4222,10 +4243,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4242,10 +4263,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4257,15 +4278,15 @@
         <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4274,7 +4295,7 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4282,10 +4303,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4294,18 +4315,18 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4322,10 +4343,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4342,10 +4363,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4357,15 +4378,15 @@
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4382,10 +4403,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4397,15 +4418,15 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4414,7 +4435,7 @@
         <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4422,10 +4443,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4434,7 +4455,7 @@
         <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4442,10 +4463,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4462,10 +4483,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4477,15 +4498,15 @@
         <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4497,15 +4518,15 @@
         <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4522,10 +4543,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4537,15 +4558,15 @@
         <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4557,15 +4578,15 @@
         <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4582,10 +4603,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4602,10 +4623,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4622,10 +4643,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4642,10 +4663,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4657,15 +4678,15 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4682,10 +4703,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4702,10 +4723,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4717,15 +4738,15 @@
         <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4734,7 +4755,7 @@
         <v>33</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>9</v>
@@ -4742,10 +4763,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4754,7 +4775,7 @@
         <v>33</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>9</v>
@@ -4762,10 +4783,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4782,10 +4803,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4802,10 +4823,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4817,15 +4838,15 @@
         <v>21</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4837,15 +4858,15 @@
         <v>21</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4862,10 +4883,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4882,10 +4903,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4894,7 +4915,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4902,19 +4923,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4922,19 +4943,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4942,10 +4963,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -4954,7 +4975,7 @@
         <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4962,10 +4983,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -4974,7 +4995,7 @@
         <v>36</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4982,10 +5003,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -4994,7 +5015,7 @@
         <v>36</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5002,10 +5023,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -5014,7 +5035,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5022,10 +5043,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -5034,7 +5055,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5042,10 +5063,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -5054,7 +5075,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5062,10 +5083,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -5074,7 +5095,7 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5082,10 +5103,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -5094,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5102,10 +5123,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -5114,18 +5135,18 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5134,7 +5155,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5142,10 +5163,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5154,7 +5175,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>9</v>
@@ -5162,19 +5183,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5182,30 +5203,30 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5214,7 +5235,7 @@
         <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5222,10 +5243,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5234,7 +5255,7 @@
         <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5242,10 +5263,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5254,7 +5275,7 @@
         <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5262,10 +5283,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5274,7 +5295,7 @@
         <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5282,10 +5303,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5294,7 +5315,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5302,10 +5323,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5314,7 +5335,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5322,10 +5343,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5334,7 +5355,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5342,10 +5363,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5354,7 +5375,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5362,10 +5383,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5374,7 +5395,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5382,10 +5403,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5394,7 +5415,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5402,10 +5423,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5414,7 +5435,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5422,10 +5443,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5434,7 +5455,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5442,19 +5463,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5462,19 +5483,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5482,10 +5503,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
@@ -5494,7 +5515,7 @@
         <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5502,10 +5523,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -5514,7 +5535,7 @@
         <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5522,10 +5543,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -5534,7 +5555,7 @@
         <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5542,10 +5563,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -5554,18 +5575,18 @@
         <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -5574,18 +5595,18 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
@@ -5594,7 +5615,7 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>9</v>
@@ -5602,10 +5623,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
@@ -5614,18 +5635,18 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
@@ -5634,18 +5655,18 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
@@ -5654,7 +5675,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5662,10 +5683,10 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
@@ -5674,7 +5695,7 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5682,10 +5703,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
@@ -5694,7 +5715,7 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5702,10 +5723,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
@@ -5714,7 +5735,7 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5722,10 +5743,10 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
@@ -5734,7 +5755,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5742,19 +5763,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5762,19 +5783,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5782,10 +5803,10 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
@@ -5794,7 +5815,7 @@
         <v>86</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5802,10 +5823,10 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
@@ -5814,7 +5835,7 @@
         <v>86</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5822,10 +5843,10 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
@@ -5834,7 +5855,7 @@
         <v>86</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5842,10 +5863,10 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
@@ -5854,7 +5875,7 @@
         <v>86</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5862,10 +5883,10 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
@@ -5874,7 +5895,7 @@
         <v>86</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5882,19 +5903,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5902,19 +5923,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5922,10 +5943,10 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
@@ -5934,7 +5955,7 @@
         <v>89</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5942,10 +5963,10 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
@@ -5954,7 +5975,7 @@
         <v>89</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5962,10 +5983,10 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
@@ -5974,7 +5995,7 @@
         <v>89</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -5982,10 +6003,10 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
@@ -5994,7 +6015,7 @@
         <v>89</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6002,10 +6023,10 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
@@ -6014,7 +6035,7 @@
         <v>89</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6022,10 +6043,10 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
@@ -6034,7 +6055,7 @@
         <v>89</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6042,10 +6063,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
@@ -6054,9 +6075,49 @@
         <v>89</v>
       </c>
       <c r="E215" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F215" s="1" t="s">
+      <c r="F217" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="464">
   <si>
     <t/>
   </si>
@@ -187,6 +187,18 @@
     <t>TWIZZ TROP.CRSH 20'S</t>
   </si>
   <si>
+    <t>20113074</t>
+  </si>
+  <si>
+    <t>MARLBORO KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20122038</t>
+  </si>
+  <si>
+    <t>MRLBORO KRT BIRU 12S</t>
+  </si>
+  <si>
     <t>10010094</t>
   </si>
   <si>
@@ -253,31 +265,31 @@
     <t>MAGNUM 234 12S</t>
   </si>
   <si>
-    <t>20113074</t>
-  </si>
-  <si>
-    <t>MARLBORO KRETEK 12'S</t>
-  </si>
-  <si>
-    <t>20122038</t>
-  </si>
-  <si>
-    <t>MRLBORO KRT BIRU 12S</t>
-  </si>
-  <si>
     <t>20132342</t>
   </si>
   <si>
     <t>DJI SAM SOE MAESTR12</t>
   </si>
   <si>
+    <t>20134530</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE SP.PRM16</t>
+  </si>
+  <si>
+    <t>20125676</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MG BIN12</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
-    <t>20134530</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE SP.PRM16</t>
+    <t>10030733</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/PRM</t>
   </si>
   <si>
     <t>15</t>
@@ -331,18 +343,6 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
-    <t>20125676</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MG BIN12</t>
-  </si>
-  <si>
-    <t>10030733</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/PRM</t>
-  </si>
-  <si>
     <t>20123283</t>
   </si>
   <si>
@@ -526,6 +526,12 @@
     <t>T/M FLTR COOL BRY16</t>
   </si>
   <si>
+    <t>20140141</t>
+  </si>
+  <si>
+    <t>DJARUM ROK.D WRP 12S</t>
+  </si>
+  <si>
     <t>20084820</t>
   </si>
   <si>
@@ -730,6 +736,18 @@
     <t>JAZY RK POPPIN16'S</t>
   </si>
   <si>
+    <t>20131551</t>
+  </si>
+  <si>
+    <t>JAZY KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20142823</t>
+  </si>
+  <si>
+    <t>JAZY MAX FILTER 12'S</t>
+  </si>
+  <si>
     <t>20095233</t>
   </si>
   <si>
@@ -1109,6 +1127,12 @@
   </si>
   <si>
     <t>CAMEL ICE LIME 16S</t>
+  </si>
+  <si>
+    <t>20143273</t>
+  </si>
+  <si>
+    <t>CAMEL KRETK KLSK 10S</t>
   </si>
   <si>
     <t>20130571</t>
@@ -1771,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2212,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2232,10 +2256,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2255,10 +2279,10 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,7 +2299,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2295,10 +2319,10 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,10 +2339,10 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2335,7 +2359,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2355,10 +2379,10 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,7 +2399,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2395,7 +2419,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2415,10 +2439,10 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,7 +2459,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2455,10 +2479,10 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,7 +2499,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2483,10 +2507,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2495,7 +2519,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2503,19 +2527,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2523,22 +2547,22 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,10 +2579,10 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2575,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2595,10 +2619,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2615,10 +2639,10 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2635,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2655,7 +2679,7 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>9</v>
@@ -2675,10 +2699,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,10 +2719,10 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,7 +2799,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2795,7 +2819,7 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3075,7 +3099,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3095,7 +3119,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3335,7 +3359,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3355,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3375,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3395,7 +3419,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3415,7 +3439,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3435,7 +3459,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3455,7 +3479,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3475,7 +3499,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3495,7 +3519,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3515,7 +3539,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3535,7 +3559,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3555,7 +3579,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3575,7 +3599,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3592,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3615,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3635,7 +3659,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3655,7 +3679,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3675,7 +3699,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3695,7 +3719,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3715,10 +3739,10 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,10 +3759,10 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3775,7 +3799,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3792,10 +3816,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3815,7 +3839,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3835,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3855,7 +3879,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3875,7 +3899,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3895,7 +3919,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3915,7 +3939,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3935,7 +3959,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3955,7 +3979,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3975,7 +3999,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3995,7 +4019,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4015,10 +4039,10 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4035,7 +4059,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4043,10 +4067,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -4055,18 +4079,18 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>248</v>
+        <v>90</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -4075,27 +4099,27 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4103,42 +4127,42 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,7 +4219,7 @@
         <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4215,7 +4239,7 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4235,7 +4259,7 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4255,7 +4279,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4275,7 +4299,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4295,7 +4319,7 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4318,7 +4342,7 @@
         <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,7 +4359,7 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4355,7 +4379,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4375,10 +4399,10 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4418,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,10 +4499,10 @@
         <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,7 +4519,7 @@
         <v>33</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4515,7 +4539,7 @@
         <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4538,7 +4562,7 @@
         <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4558,7 +4582,7 @@
         <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4578,7 +4602,7 @@
         <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,7 +4622,7 @@
         <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4618,7 +4642,7 @@
         <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,7 +4662,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4718,7 +4742,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4758,7 +4782,7 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,10 +4819,10 @@
         <v>33</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,7 +4839,7 @@
         <v>33</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>9</v>
@@ -4835,7 +4859,7 @@
         <v>33</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>9</v>
@@ -4878,7 +4902,7 @@
         <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4898,7 +4922,7 @@
         <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4918,7 +4942,7 @@
         <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,7 +4979,7 @@
         <v>33</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4972,10 +4996,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4992,10 +5016,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5012,10 +5036,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5035,7 +5059,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5055,7 +5079,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5075,7 +5099,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5095,7 +5119,7 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5115,7 +5139,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5135,7 +5159,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5155,7 +5179,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5175,10 +5199,10 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5215,10 +5239,10 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5232,13 +5256,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,10 +5276,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5272,13 +5296,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,10 +5316,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5315,7 +5339,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5335,7 +5359,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5355,7 +5379,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5375,7 +5399,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5395,7 +5419,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5415,7 +5439,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5435,7 +5459,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5455,7 +5479,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5475,7 +5499,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5495,7 +5519,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5512,10 +5536,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5532,10 +5556,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5552,10 +5576,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5572,10 +5596,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5595,7 +5619,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5615,10 +5639,10 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5635,10 +5659,10 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,10 +5679,10 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,7 +5699,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5695,10 +5719,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5715,10 +5739,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,10 +5759,10 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,7 +5779,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5775,7 +5799,7 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5795,7 +5819,7 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5812,10 +5836,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5832,10 +5856,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5852,10 +5876,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5872,10 +5896,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5892,10 +5916,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5912,10 +5936,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5932,10 +5956,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5952,10 +5976,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5972,10 +5996,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5992,10 +6016,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6012,10 +6036,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6032,10 +6056,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6052,10 +6076,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6072,10 +6096,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6092,10 +6116,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6112,12 +6136,92 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E221" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="472">
   <si>
     <t/>
   </si>
@@ -343,6 +343,18 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
+    <t>20143381</t>
+  </si>
+  <si>
+    <t>MARLBORO RED ADV20S</t>
+  </si>
+  <si>
+    <t>20143380</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD ADV20S</t>
+  </si>
+  <si>
     <t>20123283</t>
   </si>
   <si>
@@ -899,6 +911,18 @@
   </si>
   <si>
     <t>BLENDS TROPICAL 20'S</t>
+  </si>
+  <si>
+    <t>20143379</t>
+  </si>
+  <si>
+    <t>BLENDS  WTRMLN MIX20</t>
+  </si>
+  <si>
+    <t>20143382</t>
+  </si>
+  <si>
+    <t>BLENDS PASS FRTMIX20</t>
   </si>
   <si>
     <t>20135189</t>
@@ -1795,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2739,18 +2763,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2759,18 +2783,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2779,10 +2803,10 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2799,10 +2823,10 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2819,10 +2843,10 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2836,10 +2860,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2856,13 +2880,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2879,7 +2903,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2899,10 +2923,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2919,7 +2943,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2939,7 +2963,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2959,7 +2983,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2979,7 +3003,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2999,10 +3023,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3019,10 +3043,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,10 +3063,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,10 +3083,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,7 +3103,7 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3099,7 +3123,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3119,7 +3143,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3136,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3156,10 +3180,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3179,7 +3203,7 @@
         <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3199,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3219,7 +3243,7 @@
         <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3239,7 +3263,7 @@
         <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3259,7 +3283,7 @@
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3279,7 +3303,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3299,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3319,7 +3343,7 @@
         <v>21</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3339,7 +3363,7 @@
         <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3356,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3376,10 +3400,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3399,7 +3423,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3419,7 +3443,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3439,7 +3463,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3459,7 +3483,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3479,7 +3503,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3499,7 +3523,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3519,7 +3543,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3539,7 +3563,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3559,7 +3583,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3579,7 +3603,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3599,7 +3623,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3619,7 +3643,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3636,10 +3660,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3656,10 +3680,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3679,7 +3703,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3699,7 +3723,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3719,7 +3743,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3739,7 +3763,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3759,10 +3783,10 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3779,7 +3803,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3799,10 +3823,10 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,7 +3843,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3836,10 +3860,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3856,10 +3880,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3879,7 +3903,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3899,7 +3923,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3919,7 +3943,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3939,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3959,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3979,7 +4003,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3999,7 +4023,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4019,7 +4043,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4039,7 +4063,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4059,7 +4083,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4079,7 +4103,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4099,10 +4123,10 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,7 +4143,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>251</v>
+        <v>90</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4127,10 +4151,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4139,18 +4163,18 @@
         <v>30</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4159,50 +4183,50 @@
         <v>30</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,7 +4303,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4299,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4339,7 +4363,7 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4359,7 +4383,7 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4402,7 +4426,7 @@
         <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,7 +4443,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4439,10 +4463,10 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4502,7 +4526,7 @@
         <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4542,7 +4566,7 @@
         <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,7 +4583,7 @@
         <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4579,7 +4603,7 @@
         <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4599,10 +4623,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,7 +4643,7 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>9</v>
@@ -4642,7 +4666,7 @@
         <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4662,7 +4686,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4702,7 +4726,7 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4802,7 +4826,7 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4842,7 +4866,7 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4862,7 +4886,7 @@
         <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,7 +4903,7 @@
         <v>33</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>9</v>
@@ -4899,10 +4923,10 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,7 +4943,7 @@
         <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>9</v>
@@ -4939,7 +4963,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -4962,7 +4986,7 @@
         <v>21</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,7 +5006,7 @@
         <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5002,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,7 +5046,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,7 +5063,7 @@
         <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5056,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5076,10 +5100,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5096,10 +5120,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5116,10 +5140,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5139,7 +5163,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5159,7 +5183,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5179,7 +5203,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5199,7 +5223,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5219,7 +5243,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5239,7 +5263,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5259,10 +5283,10 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5279,7 +5303,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5299,10 +5323,10 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,7 +5343,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5336,13 +5360,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5356,10 +5380,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5376,13 +5400,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,10 +5420,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5419,7 +5443,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5439,7 +5463,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5459,7 +5483,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5479,7 +5503,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5499,7 +5523,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5519,7 +5543,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5539,7 +5563,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5559,7 +5583,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5579,7 +5603,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5599,7 +5623,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5616,10 +5640,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5636,10 +5660,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5656,10 +5680,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5676,10 +5700,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5699,7 +5723,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5719,10 +5743,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5739,10 +5763,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5759,10 +5783,10 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5779,7 +5803,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5799,10 +5823,10 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5819,10 +5843,10 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5839,10 +5863,10 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5859,7 +5883,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5879,7 +5903,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5899,7 +5923,7 @@
         <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5916,10 +5940,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5936,10 +5960,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5956,10 +5980,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5976,10 +6000,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5999,7 +6023,7 @@
         <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6019,7 +6043,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6039,7 +6063,7 @@
         <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6056,10 +6080,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6076,10 +6100,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6096,10 +6120,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6116,10 +6140,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6139,7 +6163,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6159,7 +6183,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6179,7 +6203,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6199,7 +6223,7 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>5</v>
@@ -6219,9 +6243,89 @@
         <v>93</v>
       </c>
       <c r="E221" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F221" s="1" t="s">
+      <c r="F225" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="462">
   <si>
     <t/>
   </si>
@@ -883,24 +883,12 @@
     <t>BLENDS PRPL.EDT 20'S</t>
   </si>
   <si>
-    <t>20136325</t>
-  </si>
-  <si>
-    <t>BLENDS BLSM.EDT 20'S</t>
-  </si>
-  <si>
     <t>20136326</t>
   </si>
   <si>
     <t>BLENDS SMMR.EDT 20'S</t>
   </si>
   <si>
-    <t>20138346</t>
-  </si>
-  <si>
-    <t>BLENDS RICH.EDT 20'S</t>
-  </si>
-  <si>
     <t>20139349</t>
   </si>
   <si>
@@ -1177,12 +1165,6 @@
     <t>WIN KRETEK BERRY 12S</t>
   </si>
   <si>
-    <t>20136051</t>
-  </si>
-  <si>
-    <t>WIN KRT NANGKA 12'S</t>
-  </si>
-  <si>
     <t>20108797</t>
   </si>
   <si>
@@ -1219,12 +1201,6 @@
     <t>ESSE BERRY POP 16'S</t>
   </si>
   <si>
-    <t>20114735</t>
-  </si>
-  <si>
-    <t>ESSE BERRY POP 12'S</t>
-  </si>
-  <si>
     <t>20093678</t>
   </si>
   <si>
@@ -1247,12 +1223,6 @@
   </si>
   <si>
     <t>JUARA  APEL 12S</t>
-  </si>
-  <si>
-    <t>20130786</t>
-  </si>
-  <si>
-    <t>JUARA  MNGGA 12S</t>
   </si>
   <si>
     <t>20095302</t>
@@ -1819,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4566,7 +4536,7 @@
         <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,7 +4556,7 @@
         <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4606,7 +4576,7 @@
         <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,10 +4593,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,10 +4613,10 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,7 +4656,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4706,7 +4676,7 @@
         <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4746,7 +4716,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,7 +4736,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4866,7 +4836,7 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4926,7 +4896,7 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,7 +4913,7 @@
         <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>9</v>
@@ -4963,7 +4933,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -5026,7 +4996,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5046,7 +5016,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5103,7 +5073,7 @@
         <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5120,10 +5090,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5140,10 +5110,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5163,7 +5133,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5183,7 +5153,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5203,7 +5173,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5223,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5243,7 +5213,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5263,7 +5233,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5283,7 +5253,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5303,7 +5273,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5323,10 +5293,10 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5343,7 +5313,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5363,7 +5333,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>9</v>
@@ -5383,7 +5353,7 @@
         <v>36</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5400,13 +5370,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,10 +5390,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5443,7 +5413,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5463,7 +5433,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5483,7 +5453,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5503,7 +5473,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5523,7 +5493,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5543,7 +5513,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5563,7 +5533,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5583,7 +5553,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5603,7 +5573,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5623,7 +5593,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5640,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5660,10 +5630,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5680,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5700,10 +5670,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5723,10 +5693,10 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5743,10 +5713,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5763,10 +5733,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5783,7 +5753,7 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5803,7 +5773,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5823,10 +5793,10 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5843,10 +5813,10 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,10 +5833,10 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5883,7 +5853,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5903,7 +5873,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5920,10 +5890,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5940,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5960,10 +5930,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5980,10 +5950,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6000,10 +5970,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6023,7 +5993,7 @@
         <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6043,7 +6013,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6060,10 +6030,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6080,10 +6050,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6100,10 +6070,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6120,10 +6090,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6140,10 +6110,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6163,7 +6133,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6183,7 +6153,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6203,7 +6173,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6223,109 +6193,9 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F225" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -295,6 +295,42 @@
     <t>15</t>
   </si>
   <si>
+    <t>10010100</t>
+  </si>
+  <si>
+    <t>MARLBORO HPACK 20'S</t>
+  </si>
+  <si>
+    <t>20107181</t>
+  </si>
+  <si>
+    <t>MARLBORO SE 20'S</t>
+  </si>
+  <si>
+    <t>20143381</t>
+  </si>
+  <si>
+    <t>MARLBORO RED ADV20S</t>
+  </si>
+  <si>
+    <t>20143380</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD ADV20S</t>
+  </si>
+  <si>
+    <t>20107184</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD SE 20S</t>
+  </si>
+  <si>
+    <t>10010102</t>
+  </si>
+  <si>
+    <t>MARLBORO LIGHT 20'S</t>
+  </si>
+  <si>
     <t>20043389</t>
   </si>
   <si>
@@ -343,16 +379,91 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
-    <t>20143381</t>
-  </si>
-  <si>
-    <t>MARLBORO RED ADV20S</t>
-  </si>
-  <si>
-    <t>20143380</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD ADV20S</t>
+    <t>20129762</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 12S</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10010090</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD 12/MRH</t>
+  </si>
+  <si>
+    <t>10010091</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MILD 16'S</t>
+  </si>
+  <si>
+    <t>20135439</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD CLS16S</t>
+  </si>
+  <si>
+    <t>20131370</t>
+  </si>
+  <si>
+    <t>SAMPOERNA ROYAL 16'S</t>
+  </si>
+  <si>
+    <t>20079512</t>
+  </si>
+  <si>
+    <t>SMPOERNA MNTHL.BR 16</t>
+  </si>
+  <si>
+    <t>20095217</t>
+  </si>
+  <si>
+    <t>SMPOERNA TRPCAL 16'S</t>
+  </si>
+  <si>
+    <t>20064088</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVOLTN 20'S</t>
+  </si>
+  <si>
+    <t>20064089</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVLT MNT 20</t>
+  </si>
+  <si>
+    <t>20138598</t>
+  </si>
+  <si>
+    <t>SMPOERN AVL RY.BRS20</t>
+  </si>
+  <si>
+    <t>20135544</t>
+  </si>
+  <si>
+    <t>MARLBORO TRPCL BS16S</t>
+  </si>
+  <si>
+    <t>20137571</t>
+  </si>
+  <si>
+    <t>TWIZZ PRIME 16'S</t>
+  </si>
+  <si>
+    <t>20139762</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM ROYAL 16S</t>
+  </si>
+  <si>
+    <t>20139763</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM TRPCL 16S</t>
   </si>
   <si>
     <t>20123283</t>
@@ -361,121 +472,10 @@
     <t>TWIZZ R/F RYL CR 16S</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
     <t>20123284</t>
   </si>
   <si>
     <t>TWIZZ YELLOW CR 16'S</t>
-  </si>
-  <si>
-    <t>20129762</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 12S</t>
-  </si>
-  <si>
-    <t>20139762</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM ROYAL 16S</t>
-  </si>
-  <si>
-    <t>20139763</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM TRPCL 16S</t>
-  </si>
-  <si>
-    <t>10010090</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD 12/MRH</t>
-  </si>
-  <si>
-    <t>10010091</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MILD 16'S</t>
-  </si>
-  <si>
-    <t>20135439</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD CLS16S</t>
-  </si>
-  <si>
-    <t>20131370</t>
-  </si>
-  <si>
-    <t>SAMPOERNA ROYAL 16'S</t>
-  </si>
-  <si>
-    <t>20079512</t>
-  </si>
-  <si>
-    <t>SMPOERNA MNTHL.BR 16</t>
-  </si>
-  <si>
-    <t>20095217</t>
-  </si>
-  <si>
-    <t>SMPOERNA TRPCAL 16'S</t>
-  </si>
-  <si>
-    <t>20064088</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVOLTN 20'S</t>
-  </si>
-  <si>
-    <t>20064089</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVLT MNT 20</t>
-  </si>
-  <si>
-    <t>20138598</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL RY.BRS20</t>
-  </si>
-  <si>
-    <t>10010100</t>
-  </si>
-  <si>
-    <t>MARLBORO HPACK 20'S</t>
-  </si>
-  <si>
-    <t>20107181</t>
-  </si>
-  <si>
-    <t>MARLBORO SE 20'S</t>
-  </si>
-  <si>
-    <t>10010102</t>
-  </si>
-  <si>
-    <t>MARLBORO LIGHT 20'S</t>
-  </si>
-  <si>
-    <t>20107184</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD SE 20S</t>
-  </si>
-  <si>
-    <t>20135544</t>
-  </si>
-  <si>
-    <t>MARLBORO TRPCL BS16S</t>
-  </si>
-  <si>
-    <t>20137571</t>
-  </si>
-  <si>
-    <t>TWIZZ PRIME 16'S</t>
   </si>
   <si>
     <t>20033460</t>
@@ -2576,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2616,7 +2616,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2636,7 +2636,7 @@
         <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2676,7 +2676,7 @@
         <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2696,7 +2696,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,7 +2716,7 @@
         <v>27</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2736,7 +2736,7 @@
         <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2756,7 +2756,7 @@
         <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2776,15 +2776,15 @@
         <v>36</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>116</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2796,15 +2796,15 @@
         <v>39</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2816,15 +2816,15 @@
         <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2836,15 +2836,15 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         <v>93</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
         <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,7 +3136,7 @@
         <v>90</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>93</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,7 +3796,7 @@
         <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5573,7 +5573,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5593,7 +5593,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="466">
   <si>
     <t/>
   </si>
@@ -544,6 +544,30 @@
     <t>DJARUM ROK.D WRP 12S</t>
   </si>
   <si>
+    <t>20139142</t>
+  </si>
+  <si>
+    <t>DJRM CGRILLOS FC 12S</t>
+  </si>
+  <si>
+    <t>20141969</t>
+  </si>
+  <si>
+    <t>DJRUM 76 APL RYL 12S</t>
+  </si>
+  <si>
+    <t>20143815</t>
+  </si>
+  <si>
+    <t>FORTE FUJI APPLE20S</t>
+  </si>
+  <si>
+    <t>20143814</t>
+  </si>
+  <si>
+    <t>FORTE HOKAIDO MLN20S</t>
+  </si>
+  <si>
     <t>20084820</t>
   </si>
   <si>
@@ -614,18 +638,6 @@
   </si>
   <si>
     <t>DJARUM SUPER WRAP12S</t>
-  </si>
-  <si>
-    <t>20139142</t>
-  </si>
-  <si>
-    <t>DJRM CGRILLOS FC 12S</t>
-  </si>
-  <si>
-    <t>20141969</t>
-  </si>
-  <si>
-    <t>DJRUM 76 APL RYL 12S</t>
   </si>
   <si>
     <t>10010081</t>
@@ -1789,7 +1801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F220"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3390,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3410,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3433,7 +3445,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3453,7 +3465,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3473,7 +3485,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3493,7 +3505,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3513,7 +3525,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3533,7 +3545,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3553,7 +3565,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3573,7 +3585,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3593,7 +3605,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3613,7 +3625,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3633,7 +3645,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3653,7 +3665,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3670,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3690,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3713,7 +3725,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3733,7 +3745,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3753,7 +3765,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3773,7 +3785,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3793,10 +3805,10 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3833,10 +3845,10 @@
         <v>27</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,7 +3865,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3870,10 +3882,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3890,10 +3902,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3913,7 +3925,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3933,7 +3945,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3953,7 +3965,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3973,7 +3985,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3993,7 +4005,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4013,7 +4025,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4033,7 +4045,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4053,7 +4065,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4073,7 +4085,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4093,7 +4105,7 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4113,7 +4125,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4133,10 +4145,10 @@
         <v>30</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,7 +4165,7 @@
         <v>30</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>255</v>
+        <v>90</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4161,10 +4173,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4173,18 +4185,18 @@
         <v>30</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>258</v>
+        <v>93</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4193,50 +4205,50 @@
         <v>30</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4325,7 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4333,7 +4345,7 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4373,7 +4385,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4393,7 +4405,7 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4436,7 +4448,7 @@
         <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,7 +4465,7 @@
         <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4473,10 +4485,10 @@
         <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4556,7 +4568,7 @@
         <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4576,7 +4588,7 @@
         <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,10 +4605,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4613,10 +4625,10 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4656,7 +4668,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4676,7 +4688,7 @@
         <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4716,7 +4728,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4736,7 +4748,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4836,7 +4848,7 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4896,7 +4908,7 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,7 +4925,7 @@
         <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>9</v>
@@ -4933,7 +4945,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -4996,7 +5008,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5016,7 +5028,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,7 +5085,7 @@
         <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5090,10 +5102,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5110,10 +5122,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5133,7 +5145,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5153,7 +5165,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5173,7 +5185,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5193,7 +5205,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5213,7 +5225,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5233,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5253,7 +5265,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5273,7 +5285,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5293,10 +5305,10 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,7 +5325,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5333,7 +5345,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>9</v>
@@ -5353,7 +5365,7 @@
         <v>36</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5370,13 +5382,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5390,10 +5402,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5413,7 +5425,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5433,7 +5445,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5453,7 +5465,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5473,7 +5485,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5493,7 +5505,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5513,7 +5525,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5533,7 +5545,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5553,7 +5565,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5573,7 +5585,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5593,7 +5605,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5610,10 +5622,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5630,10 +5642,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5653,7 +5665,7 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5673,7 +5685,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5693,10 +5705,10 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,10 +5725,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,7 +5745,7 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>9</v>
@@ -5753,10 +5765,10 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,10 +5785,10 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,7 +5805,7 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5813,7 +5825,7 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5833,7 +5845,7 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5853,7 +5865,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5873,7 +5885,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5890,10 +5902,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5910,10 +5922,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5933,7 +5945,7 @@
         <v>90</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5953,7 +5965,7 @@
         <v>90</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5973,7 +5985,7 @@
         <v>90</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5993,7 +6005,7 @@
         <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6013,7 +6025,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6030,10 +6042,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6050,10 +6062,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6073,7 +6085,7 @@
         <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6093,7 +6105,7 @@
         <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6113,7 +6125,7 @@
         <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6133,7 +6145,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6153,7 +6165,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6173,7 +6185,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6193,9 +6205,49 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F220" s="1" t="s">
+      <c r="F222" s="1" t="s">
         <v>5</v>
       </c>
     </row>
